--- a/Luban/Config/Datas/Levels/L21/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L21/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L21 W1/25; N=51; EHP=325.380000; normal:17x25,normal:18x26</t>
+          <t>L21 W1/25; N=51; EHP=851.674586; normal:17x25,normal:18x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L21 W2/25; N=57; EHP=380.788386; normal:17x29,normal:18x28</t>
+          <t>L21 W2/25; N=57; EHP=996.704748; normal:17x29,normal:18x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10018526,10018528,10048670,10018526,10018528,10048670,10018526,10018528,10048671,10018526,10018528,10048672,10018526,10018528,10048672,10018526,10018528,10048673,10018526,10018528,10048673,10018526,10018528,10048674,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018526,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527</t>
+          <t>10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018528,10018526,10018526,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018527,10018526,10018526,10018526,10018526,10018526,10018526,10018526,10018526</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L21 W3/25; N=63; EHP=465.607296; air:2x2,air:11x1,air:12x2,air:13x2,air:14x1,normal:17x19,normal:18x19,swarm:84x17</t>
+          <t>L21 W3/25; N=63; EHP=1320.565306; normal:17x27,normal:18x19,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10018529,10018531,10048675,10018529,10018531,10048675,10018529,10018531,10048676,10018529,10018531,10048676,10018529,10018531,10048677,10018529,10018531,10048678,10018529,10018531,10048678,10018529,10018531,10048679,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018529,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530</t>
+          <t>10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018531,10018529,10018529,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018530,10018529,10018529,10018529,10018529,10018529,10018529,10018529,10018529</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L21 W4/25; N=69; EHP=587.209458; air:2x2,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x21,normal:18x21,swarm:84x19</t>
+          <t>L21 W4/25; N=69; EHP=1653.708249; normal:17x29,normal:18x21,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10018532,10018535,10048680,10018534,10018532,10018535,10048681,10018534,10018532,10018535,10048681,10018534,10018532,10018535,10048682,10018534,10018532,10018535,10048682,10018536,10018532,10018535,10048683,10018536,10018532,10018535,10048683,10018536,10018532,10018535,10048684,10018536,10018532,10018535,10048684,10018537,10018532,10018535,10018537,10018532,10018535,10018537,10018532,10018535,10018532,10018535,10018532,10018535,10018532,10018535,10018532,10018535,10018532,10018535,10018533,10018535,10018533,10018535,10018533,10018535,10018533,10018535,10018533,10018533,10018533,10018533,10018533,10018533,10018533,10018533,10018533,10018533,10018533,10018533,10018533</t>
+          <t>10018532,10048680,10048680,10018534,10018532,10048681,10048681,10018534,10018532,10048681,10048681,10018534,10018532,10048682,10048682,10018534,10018532,10048682,10048682,10018536,10018532,10048683,10048683,10018536,10018532,10048683,10048683,10018536,10018532,10048684,10048684,10018536,10018532,10048684,10048684,10018537,10018532,10018535,10018537,10018532,10018535,10018537,10018532,10018535,10018532,10018535,10018532,10018535,10018532,10018535,10018532,10018535,10018532,10018535,10018533,10018535,10018533,10018535,10018533,10018535,10018533,10018535,10018533,10018533,10018533,10018533,10018533,10018533,10018533,10018533,10018533,10018533,10018533,10018533,10018533</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L21 W5/25; N=75; EHP=1099.332696; air:2x1,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x17,normal:18x17,medium:83x4,swarm:84x21,medium:108x4,medium:123x3</t>
+          <t>L21 W5/25; N=75; EHP=2914.263713; air:2x2,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x4,medium:108x4,medium:123x3,normal:17x17,normal:18x17,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>10018541,10018547,10018543,10048685,10018546,10018541,10018547,10018543,10048685,10018546,10018541,10018547,10018544,10018538,10018546,10018541,10018547,10018544,10018538,10018546,10018541,10018547,10018545,10048686,10018549,10018541,10018547,10018545,10048686,10018549,10018541,10018547,10018545,10018539,10018549,10018541,10018547,10018548,10018539,10018549,10018541,10018547,10018548,10018540,10018550,10018541,10018547,10018540,10018550,10018541,10018547,10018550,10018541,10018547,10018550,10018541,10018547,10018541,10018547,10018542,10018547,10018542,10018547,10018542,10018547,10018542,10018547,10018542,10018547,10018542,10018547,10018542,10018547,10018542,10018547,10018542,10018542,10018542,10018542,10018542,10018542</t>
+          <t>10018541,10048685,10018543,10048685,10018546,10018541,10048685,10018543,10048685,10018546,10018541,10018538,10018544,10018538,10018546,10018541,10018538,10018544,10018538,10018546,10018541,10048686,10018545,10048686,10018549,10018541,10048686,10018545,10048686,10018549,10018541,10018539,10018545,10018539,10018549,10018541,10018539,10018548,10018539,10018549,10018541,10018540,10018548,10018540,10018550,10018541,10018540,10018540,10018550,10018541,10018547,10018550,10018541,10018547,10018550,10018541,10018547,10018541,10018547,10018542,10018547,10018542,10018547,10018542,10018547,10018542,10018547,10018542,10018547,10018542,10018547,10018542,10018547,10018542,10018547,10018542,10018542,10018542,10018542,10018542,10018542</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L21 W6/25; N=81; EHP=1122.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x14,normal:18x14,fast:30x2,fast:58x2,fast:64x3,medium:83x4,swarm:84x22,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L21 W6/25; N=81; EHP=2976.044840; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x2,fast:64x3,fast:98x2,medium:83x4,medium:108x4,medium:123x4,normal:17x14,normal:18x14,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>10018554,10018560,10018556,10048687,10018559,10018554,10018560,10018556,10048687,10018559,10018554,10018560,10018556,10018551,10018559,10018554,10018560,10018557,10018551,10018559,10018554,10018560,10018557,10048688,10018562,10018554,10018560,10018558,10048688,10018562,10018554,10018560,10018558,10018552,10018562,10018554,10018560,10018561,10018552,10018562,10018554,10018560,10018561,10018553,10018563,10018554,10018560,10018561,10018553,10018563,10018554,10018560,10018563,10018554,10018560,10018563,10018554,10018560,10018563,10018554,10018560,10018554,10018560,10018555,10018560,10018555,10018560,10018555,10018560,10018555,10018560,10018555,10018560,10018555,10018560,10018555,10018560,10018555,10018560,10018555,10018560,10018555,10018555,10018555,10018555,10018555,10018555</t>
+          <t>10018554,10048687,10018556,10048687,10018559,10018554,10048687,10018556,10048687,10018559,10018554,10018551,10018556,10018551,10018559,10018554,10018551,10018557,10018551,10018559,10018554,10048688,10018557,10048688,10018562,10018554,10048688,10018558,10048688,10018562,10018554,10018552,10018558,10018552,10018562,10018554,10018552,10018561,10018552,10018562,10018554,10018553,10018561,10018553,10018563,10018554,10018553,10018561,10018553,10018563,10018554,10018560,10018563,10018554,10018560,10018563,10018554,10018560,10018563,10018554,10018560,10018554,10018560,10018555,10018560,10018555,10018560,10018555,10018560,10018555,10018560,10018555,10018560,10018555,10018560,10018555,10018560,10018555,10018560,10018555,10018560,10018555,10018555,10018555,10018555,10018555,10018555</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L21 W7/25; N=87; EHP=1258.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x3,fast:58x2,fast:64x2,medium:83x4,swarm:84x24,fast:98x3,medium:108x4,medium:123x5</t>
+          <t>L21 W7/25; N=87; EHP=3333.588552; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x2,fast:98x3,medium:83x4,medium:108x4,medium:123x5,normal:17x15,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>10018567,10018573,10018569,10048689,10018572,10018567,10018573,10018569,10048689,10018572,10018567,10018573,10018570,10018564,10018572,10018567,10018573,10018570,10018564,10018572,10018567,10018573,10018570,10048690,10018575,10018567,10018573,10018571,10048690,10018575,10018567,10018573,10018571,10048690,10018575,10018567,10018573,10018571,10018565,10018575,10018567,10018573,10018574,10018565,10018575,10018567,10018573,10018574,10018566,10018576,10018567,10018573,10018574,10018566,10018576,10018567,10018573,10018576,10018567,10018573,10018576,10018567,10018573,10018567,10018573,10018567,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018568,10018568,10018568,10018568,10018568</t>
+          <t>10018567,10048689,10018569,10048689,10018572,10018567,10048689,10018569,10048689,10018572,10018567,10018564,10018570,10018564,10018572,10018567,10018564,10018570,10018564,10018572,10018567,10048690,10018570,10048690,10018575,10018567,10048690,10018571,10048690,10018575,10018567,10048690,10018571,10048690,10018575,10018567,10018565,10018571,10018565,10018575,10018567,10018565,10018574,10018565,10018575,10018567,10018566,10018574,10018566,10018576,10018567,10018566,10018574,10018566,10018576,10018567,10018573,10018576,10018567,10018573,10018576,10018567,10018573,10018567,10018573,10018567,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018573,10018568,10018568,10018568,10018568,10018568,10018568</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L21 W8/25; N=93; EHP=1617.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x16,normal:18x16,fast:30x2,fast:58x3,fast:64x3,medium:83x4,swarm:84x26,fast:98x3,medium:108x5,medium:123x4</t>
+          <t>L21 W8/25; N=93; EHP=4287.040283; air:2x4,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x3,fast:98x3,medium:83x4,medium:108x5,medium:123x4,normal:17x16,normal:18x16,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>10018580,10018586,10018582,10048691,10018585,10018580,10018586,10018582,10048691,10018585,10018580,10018586,10018582,10048691,10018585,10018580,10018586,10018583,10018577,10018585,10018580,10018586,10018583,10018577,10018585,10018580,10018586,10018583,10048692,10018588,10018580,10018586,10018584,10048692,10018588,10018580,10018586,10018584,10018578,10018588,10018580,10018586,10018584,10018578,10018588,10018580,10018586,10018587,10018578,10018589,10018580,10018586,10018587,10018579,10018589,10018580,10018586,10018579,10018589,10018580,10018586,10018589,10018580,10018586,10018589,10018580,10018586,10018580,10018586,10018580,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018581,10018581,10018581,10018581,10018581,10018581,10018581</t>
+          <t>10018580,10048691,10018582,10048691,10018585,10018580,10048691,10018582,10048691,10018585,10018580,10048691,10018582,10048691,10018585,10018580,10018577,10018583,10018577,10018585,10018580,10018577,10018583,10018577,10018585,10018580,10048692,10018583,10048692,10018588,10018580,10048692,10018584,10048692,10018588,10018580,10018578,10018584,10018578,10018588,10018580,10018578,10018584,10018578,10018588,10018580,10018578,10018587,10018578,10018589,10018580,10018579,10018587,10018579,10018589,10018580,10018579,10018579,10018589,10018580,10018586,10018589,10018580,10018586,10018589,10018580,10018586,10018580,10018586,10018580,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018586,10018581,10018581,10018581,10018581,10018581,10018581,10018581,10018581</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L21 W9/25; N=99; EHP=2063.000000; air:2x3,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x18,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x27,fast:98x2,medium:108x4,medium:123x5</t>
+          <t>L21 W9/25; N=99; EHP=5470.983250; air:2x6,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x2,medium:83x5,medium:108x4,medium:123x5,normal:17x17,normal:18x18,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>10018593,10018599,10018595,10048693,10018598,10018593,10018599,10018595,10048693,10018598,10018593,10018599,10018595,10018590,10018598,10018593,10018599,10018596,10018590,10018598,10018593,10018599,10018596,10018590,10018598,10018593,10018599,10018596,10048694,10018601,10018593,10018599,10018597,10048694,10018601,10018593,10018599,10018597,10018591,10018601,10018593,10018599,10018597,10018591,10018601,10018593,10018599,10018600,10018591,10018601,10018593,10018599,10018600,10018592,10018602,10018593,10018599,10018600,10018592,10018602,10018593,10018599,10018592,10018602,10018593,10018599,10018602,10018593,10018599,10018602,10018593,10018599,10018593,10018599,10018593,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018594,10018594,10018594,10018594,10018594,10018594</t>
+          <t>10018593,10048693,10018595,10048693,10018598,10018593,10048693,10018595,10048693,10018598,10018593,10018590,10018595,10018590,10018598,10018593,10018590,10018596,10018590,10018598,10018593,10018590,10018596,10018590,10018598,10018593,10048694,10018596,10048694,10018601,10018593,10048694,10018597,10048694,10018601,10018593,10018591,10018597,10018591,10018601,10018593,10018591,10018597,10018591,10018601,10018593,10018591,10018600,10018591,10018601,10018593,10018592,10018600,10018592,10018602,10018593,10018592,10018600,10018592,10018602,10018593,10018592,10018592,10018602,10018593,10018599,10018602,10018593,10018599,10018602,10018593,10018599,10018593,10018599,10018593,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018599,10018594,10018594,10018594,10018594,10018594,10018594,10018594</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L21 W10/25; N=105; EHP=3803.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x18,normal:18x18,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x29,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L21 W10/25; N=105; EHP=10088.502091; air:2x4,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x18,normal:18x18,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>10018603,10018612,10018605,10048695,10018611,10018606,10018603,10018612,10018605,10048695,10018611,10018607,10018603,10018612,10018605,10048696,10018611,10045204,10018603,10018612,10018605,10048696,10018611,10045205,10018603,10018612,10018608,10048696,10018611,10018610,10018603,10018612,10018608,10048697,10018616,10018610,10018603,10018612,10018608,10048697,10018616,10018613,10018603,10018612,10018609,10048697,10018616,10018613,10018603,10018612,10018609,10048698,10018616,10018614,10018603,10018612,10018609,10048698,10018616,10018614,10018603,10018612,10018615,10048699,10018616,10045206,10018603,10018612,10018615,10048699,10018617,10018603,10018612,10018615,10048699,10018617,10018604,10018612,10018617,10018604,10018612,10018617,10018604,10018612,10018617,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018612,10018612,10018612,10018612</t>
+          <t>10018603,10048695,10018605,10048695,10018611,10018606,10018603,10048695,10018605,10048695,10018611,10018607,10018603,10048696,10018605,10048696,10018611,10045204,10018603,10048696,10018605,10048696,10018611,10045205,10018603,10048696,10018608,10048696,10018611,10018610,10018603,10048697,10018608,10048697,10018616,10018610,10018603,10048697,10018608,10048697,10018616,10018613,10018603,10048697,10018609,10048697,10018616,10018613,10018603,10048698,10018609,10048698,10018616,10018614,10018603,10048698,10018609,10048698,10018616,10018614,10018603,10048699,10018615,10048699,10018616,10045206,10018603,10048699,10018615,10048699,10018617,10018603,10048699,10018615,10048699,10018617,10018604,10018612,10018617,10018604,10018612,10018617,10018604,10018612,10018617,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018604,10018612,10018612,10018612,10018612,10018612</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L21 W11/25; N=111; EHP=3880.000000; air:2x2,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x13,normal:18x14,fast:30x4,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x5,swarm:84x31,heavy:86x2,heavy:88x2,fast:98x3,medium:108x6,medium:123x5,heavy:127x1</t>
+          <t>L21 W11/25; N=111; EHP=10270.167121; air:2x4,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x4,fast:58x3,fast:64x3,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x5,medium:108x6,medium:123x5,normal:17x13,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>10018621,10018631,10018623,10048700,10018630,10018624,10018621,10018631,10018623,10048700,10018630,10018624,10018621,10018631,10018623,10048700,10018630,10018625,10018621,10018631,10018626,10018618,10018630,10045207,10018621,10018631,10018626,10018618,10018630,10018628,10018621,10018631,10018626,10048701,10018630,10018629,10018621,10018631,10018626,10048701,10018634,10018629,10018621,10018631,10018627,10048701,10018634,10018632,10018621,10018631,10018627,10018619,10018634,10018632,10018621,10018631,10018627,10018619,10018634,10045208,10018621,10018631,10018633,10018619,10018634,10018636,10018621,10018631,10018633,10018620,10018635,10018621,10018631,10018633,10018620,10018635,10018621,10018631,10018633,10018620,10018635,10018621,10018631,10018635,10018622,10018631,10018635,10018622,10018631,10018635,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018631,10018631,10018631</t>
+          <t>10018621,10048700,10018623,10048700,10018630,10018624,10018621,10048700,10018623,10048700,10018630,10018624,10018621,10048700,10018623,10048700,10018630,10018625,10018621,10018618,10018626,10018618,10018630,10045207,10018621,10018618,10018626,10018618,10018630,10018628,10018621,10048701,10018626,10048701,10018630,10018629,10018621,10048701,10018626,10048701,10018634,10018629,10018621,10048701,10018627,10048701,10018634,10018632,10018621,10018619,10018627,10018619,10018634,10018632,10018621,10018619,10018627,10018619,10018634,10045208,10018621,10018619,10018633,10018619,10018634,10018636,10018621,10018620,10018633,10018620,10018635,10018621,10018620,10018633,10018620,10018635,10018621,10018620,10018633,10018620,10018635,10018621,10018631,10018635,10018622,10018631,10018635,10018622,10018631,10018635,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018622,10018631,10018631,10018631,10018631</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L21 W12/25; N=117; EHP=4015.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x14,fast:30x3,heavy:31x2,heavy:40x1,fast:58x4,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x32,heavy:86x2,heavy:88x1,fast:98x4,medium:108x5,medium:123x6,heavy:127x1</t>
+          <t>L21 W12/25; N=117; EHP=10630.662447; air:2x6,air:11x4,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x3,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x6,medium:108x5,medium:123x6,normal:17x15,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>10018640,10018650,10018642,10048702,10018649,10018643,10018640,10018650,10018642,10048702,10018649,10018643,10018640,10018650,10018642,10048702,10018649,10018644,10018640,10018650,10018645,10018637,10018649,10018644,10018640,10018650,10018645,10018637,10018649,10018647,10018640,10018650,10018645,10018637,10018649,10018648,10018640,10018650,10018645,10048703,10018653,10045209,10018640,10018650,10018646,10048703,10018653,10018651,10018640,10018650,10018646,10048703,10018653,10018651,10018640,10018650,10018646,10018638,10018653,10045210,10018640,10018650,10018646,10018638,10018653,10018655,10018640,10018650,10018652,10018638,10018653,10018655,10018640,10018650,10018652,10018639,10018654,10018640,10018650,10018652,10018639,10018654,10018640,10018650,10018639,10018654,10018641,10018650,10018654,10018641,10018650,10018654,10018641,10018650,10018654,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018650,10018650,10018650,10018650</t>
+          <t>10018640,10048702,10018642,10048702,10018649,10018643,10018640,10048702,10018642,10048702,10018649,10018643,10018640,10048702,10018642,10048702,10018649,10018644,10018640,10018637,10018645,10018637,10018649,10018644,10018640,10018637,10018645,10018637,10018649,10018647,10018640,10018637,10018645,10018637,10018649,10018648,10018640,10048703,10018645,10048703,10018653,10045209,10018640,10048703,10018646,10048703,10018653,10018651,10018640,10048703,10018646,10048703,10018653,10018651,10018640,10018638,10018646,10018638,10018653,10045210,10018640,10018638,10018646,10018638,10018653,10018655,10018640,10018638,10018652,10018638,10018653,10018655,10018640,10018639,10018652,10018639,10018654,10018640,10018639,10018652,10018639,10018654,10018640,10018639,10018639,10018654,10018641,10018650,10018654,10018641,10018650,10018654,10018641,10018650,10018654,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018641,10018650,10018650,10018650,10018650,10018650</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L21 W13/25; N=123; EHP=4898.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x15,fast:30x3,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x6,swarm:84x34,heavy:86x2,heavy:88x1,fast:98x3,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L21 W13/25; N=123; EHP=12970.934220; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>10018659,10018669,10018661,10048704,10018668,10018662,10018659,10018669,10018661,10048704,10018668,10018662,10018659,10018669,10018661,10048704,10018668,10018663,10018659,10018669,10018661,10018656,10018668,10018663,10018659,10018669,10018664,10018656,10018668,10018666,10018659,10018669,10018664,10018656,10018668,10018667,10018659,10018669,10018664,10048705,10018672,10018667,10018659,10018669,10018665,10048705,10018672,10045211,10018659,10018669,10018665,10048705,10018672,10045212,10018659,10018669,10018665,10018657,10018672,10018670,10018659,10018669,10018665,10018657,10018672,10018674,10018659,10018669,10018671,10018657,10018672,10018674,10018659,10018669,10018671,10018658,10018672,10018659,10018669,10018671,10018658,10018673,10018659,10018669,10018671,10018658,10018673,10018659,10018669,10018673,10018660,10018669,10018673,10018660,10018669,10018673,10018660,10018669,10018673,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018669,10018669,10018669,10018669</t>
+          <t>10018659,10048704,10018661,10048704,10018668,10018662,10018659,10048704,10018661,10048704,10018668,10018662,10018659,10048704,10018661,10048704,10018668,10018663,10018659,10018656,10018661,10018656,10018668,10018663,10018659,10018656,10018664,10018656,10018668,10018666,10018659,10018656,10018664,10018656,10018668,10018667,10018659,10048705,10018664,10048705,10018672,10018667,10018659,10048705,10018665,10048705,10018672,10045211,10018659,10048705,10018665,10048705,10018672,10045212,10018659,10018657,10018665,10018657,10018672,10018670,10018659,10018657,10018665,10018657,10018672,10018674,10018659,10018657,10018671,10018657,10018672,10018674,10018659,10018658,10018671,10018658,10018672,10018659,10018658,10018671,10018658,10018673,10018659,10018658,10018671,10018658,10018673,10018659,10018669,10018673,10018660,10018669,10018673,10018660,10018669,10018673,10018660,10018669,10018673,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018660,10018669,10018669,10018669,10018669,10018669</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L21 W14/25; N=129; EHP=5907.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x16,fast:30x4,heavy:31x2,heavy:40x2,fast:58x3,fast:64x4,heavy:67x1,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x36,heavy:86x1,heavy:88x1,fast:98x4,medium:108x7,medium:123x6,heavy:127x2</t>
+          <t>L21 W14/25; N=129; EHP=15635.029135; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x7,medium:123x6,normal:17x16,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>10018678,10018689,10018680,10048706,10018688,10045213,10018684,10018678,10018689,10018680,10048706,10018688,10018681,10018678,10018689,10018680,10048706,10018688,10018681,10018678,10018689,10018680,10018675,10018688,10018685,10018678,10018689,10018682,10018675,10018688,10018685,10018678,10018689,10018682,10018675,10018688,10018686,10018678,10018689,10018682,10048707,10018688,10018686,10018678,10018689,10018682,10048707,10018692,10018687,10018678,10018689,10018683,10048707,10018692,10045214,10018678,10018689,10018683,10018676,10018692,10018690,10018678,10018689,10018683,10018676,10018692,10018690,10018678,10018689,10018683,10018676,10018692,10018694,10018678,10018689,10018691,10018676,10018692,10018694,10018678,10018689,10018691,10018677,10018693,10018678,10018689,10018691,10018677,10018693,10018678,10018689,10018691,10018677,10018693,10018679,10018689,10018693,10018679,10018689,10018693,10018679,10018689,10018693,10018679,10018689,10018693,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018689,10018689,10018689,10018689,10018689</t>
+          <t>10018678,10048706,10018680,10048706,10018688,10045213,10018684,10018678,10048706,10018680,10048706,10018688,10018681,10018678,10048706,10018680,10048706,10018688,10018681,10018678,10018675,10018680,10018675,10018688,10018685,10018678,10018675,10018682,10018675,10018688,10018685,10018678,10018675,10018682,10018675,10018688,10018686,10018678,10048707,10018682,10048707,10018688,10018686,10018678,10048707,10018682,10048707,10018692,10018687,10018678,10048707,10018683,10048707,10018692,10045214,10018678,10018676,10018683,10018676,10018692,10018690,10018678,10018676,10018683,10018676,10018692,10018690,10018678,10018676,10018683,10018676,10018692,10018694,10018678,10018676,10018691,10018676,10018692,10018694,10018678,10018677,10018691,10018677,10018693,10018678,10018677,10018691,10018677,10018693,10018678,10018677,10018691,10018677,10018693,10018679,10018689,10018693,10018679,10018689,10018693,10018679,10018689,10018693,10018679,10018689,10018693,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018679,10018689,10018689,10018689,10018689,10018689,10018689</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L21 W15/25; N=135; EHP=10310.000000; air:2x3,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x16,normal:18x16,fast:30x4,heavy:31x1,heavy:40x2,fast:58x4,fast:64x4,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x37,heavy:86x1,heavy:88x2,fast:98x4,medium:108x6,medium:123x7,heavy:127x2</t>
+          <t>L21 W15/25; N=135; EHP=27285.512158; air:2x6,air:11x6,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x7,medium:108x6,medium:123x7,normal:17x16,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>10018695,10018704,10018697,10048708,10018703,10045215,10018695,10018704,10018697,10048708,10018703,10045216,10018695,10018704,10018697,10048708,10018703,10018700,10018695,10018704,10018697,10048709,10018703,10018700,10018695,10018704,10018698,10048709,10018703,10018701,10018695,10018704,10018698,10048709,10018703,10018701,10018695,10018704,10018698,10048709,10018703,10018702,10018695,10018704,10018698,10048710,10018708,10018702,10018695,10018704,10018699,10048710,10018708,10018705,10018695,10018704,10018699,10048710,10018708,10018705,10018695,10018704,10018699,10048711,10018708,10018706,10018695,10018704,10018699,10048711,10018708,10018706,10018695,10018704,10018707,10048711,10018708,10018710,10018695,10018704,10018707,10048712,10018708,10018710,10018695,10018704,10018707,10048712,10018709,10018695,10018704,10018707,10048712,10018709,10018695,10018704,10048712,10018709,10018696,10018704,10018709,10018696,10018704,10018709,10018696,10018704,10018709,10018696,10018704,10018709,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018704,10018704,10018704,10018704,10018704</t>
+          <t>10018695,10048708,10018697,10048708,10018703,10045215,10018695,10048708,10018697,10048708,10018703,10045216,10018695,10048708,10018697,10048708,10018703,10018700,10018695,10048709,10018697,10048709,10018703,10018700,10018695,10048709,10018698,10048709,10018703,10018701,10018695,10048709,10018698,10048709,10018703,10018701,10018695,10048709,10018698,10048709,10018703,10018702,10018695,10048710,10018698,10048710,10018708,10018702,10018695,10048710,10018699,10048710,10018708,10018705,10018695,10048710,10018699,10048710,10018708,10018705,10018695,10048711,10018699,10048711,10018708,10018706,10018695,10048711,10018699,10048711,10018708,10018706,10018695,10048711,10018707,10048711,10018708,10018710,10018695,10048712,10018707,10048712,10018708,10018710,10018695,10048712,10018707,10048712,10018709,10018695,10048712,10018707,10048712,10018709,10018695,10048712,10048712,10018709,10018696,10018704,10018709,10018696,10018704,10018709,10018696,10018704,10018709,10018696,10018704,10018709,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018696,10018704,10018704,10018704,10018704,10018704,10018704</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L21 W16/25; N=141; EHP=10517.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x4,normal:17x17,normal:18x17,fast:30x4,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x39,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L21 W16/25; N=141; EHP=27846.137644; air:2x6,air:11x8,air:12x6,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>10018714,10018725,10018716,10048713,10018724,10018717,10018714,10018725,10018716,10048713,10018724,10018717,10018714,10018725,10018716,10048713,10018724,10018718,10018714,10018725,10018716,10048713,10018724,10018721,10018714,10018725,10018719,10018711,10018724,10018721,10018714,10018725,10018719,10018711,10018724,10018722,10018714,10018725,10018719,10018711,10018724,10018722,10018714,10018725,10018719,10048714,10018729,10018723,10018714,10018725,10018719,10048714,10018729,10018723,10018714,10018725,10018720,10048714,10018729,10018726,10018714,10018725,10018720,10048714,10018729,10018726,10018714,10018725,10018720,10018712,10018729,10018727,10018714,10018725,10018720,10018712,10018729,10018727,10018714,10018725,10018728,10018712,10018729,10045217,10018714,10018725,10018728,10018713,10018729,10018714,10018725,10018728,10018713,10018730,10018714,10018725,10018728,10018713,10018730,10018715,10018725,10018713,10018730,10018715,10018725,10018730,10018715,10018725,10018730,10018715,10018725,10018730,10018715,10018725,10018730,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018725,10018725,10018725,10018725,10018725,10018725</t>
+          <t>10018714,10048713,10018716,10048713,10018724,10018717,10018714,10048713,10018716,10048713,10018724,10018717,10018714,10048713,10018716,10048713,10018724,10018718,10018714,10048713,10018716,10048713,10018724,10018721,10018714,10018711,10018719,10018711,10018724,10018721,10018714,10018711,10018719,10018711,10018724,10018722,10018714,10018711,10018719,10018711,10018724,10018722,10018714,10048714,10018719,10048714,10018729,10018723,10018714,10048714,10018719,10048714,10018729,10018723,10018714,10048714,10018720,10048714,10018729,10018726,10018714,10048714,10018720,10048714,10018729,10018726,10018714,10018712,10018720,10018712,10018729,10018727,10018714,10018712,10018720,10018712,10018729,10018727,10018714,10018712,10018728,10018712,10018729,10045217,10018714,10018713,10018728,10018713,10018729,10018714,10018713,10018728,10018713,10018730,10018714,10018713,10018728,10018713,10018730,10018715,10018713,10018713,10018730,10018715,10018725,10018730,10018715,10018725,10018730,10018715,10018725,10018730,10018715,10018725,10018730,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018715,10018725,10018725,10018725,10018725,10018725,10018725,10018725</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L21 W17/25; N=147; EHP=10728.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x17,normal:18x18,fast:30x4,heavy:31x2,heavy:40x1,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x41,heavy:86x2,heavy:88x2,fast:98x4,medium:108x8,medium:123x7,heavy:127x1</t>
+          <t>L21 W17/25; N=147; EHP=28411.947577; air:2x8,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x5,fast:64x4,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x8,medium:123x7,normal:17x17,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>10018734,10018744,10018736,10048715,10018743,10018737,10018734,10018744,10018736,10048715,10018743,10018737,10018734,10018744,10018736,10048715,10018743,10018738,10018734,10018744,10018736,10048715,10018743,10018738,10018734,10018744,10018736,10018731,10018743,10018741,10018734,10018744,10018739,10018731,10018743,10018741,10018734,10018744,10018739,10018731,10018743,10045218,10018734,10018744,10018739,10048716,10018743,10018742,10018734,10018744,10018739,10048716,10018748,10018742,10018734,10018744,10018740,10048716,10018748,10018745,10018734,10018744,10018740,10048716,10018748,10018745,10018734,10018744,10018740,10018732,10018748,10018746,10018734,10018744,10018740,10018732,10018748,10018746,10018734,10018744,10018740,10018732,10018748,10018750,10018734,10018744,10018747,10018732,10018748,10018750,10018734,10018744,10018747,10018733,10018749,10018734,10018744,10018747,10018733,10018749,10018734,10018744,10018747,10018733,10018749,10018734,10018744,10018749,10018735,10018744,10018749,10018735,10018744,10018749,10018735,10018744,10018749,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018744,10018744,10018744,10018744</t>
+          <t>10018734,10048715,10018736,10048715,10018743,10018737,10018734,10048715,10018736,10048715,10018743,10018737,10018734,10048715,10018736,10048715,10018743,10018738,10018734,10048715,10018736,10048715,10018743,10018738,10018734,10018731,10018736,10018731,10018743,10018741,10018734,10018731,10018739,10018731,10018743,10018741,10018734,10018731,10018739,10018731,10018743,10045218,10018734,10048716,10018739,10048716,10018743,10018742,10018734,10048716,10018739,10048716,10018748,10018742,10018734,10048716,10018740,10048716,10018748,10018745,10018734,10048716,10018740,10048716,10018748,10018745,10018734,10018732,10018740,10018732,10018748,10018746,10018734,10018732,10018740,10018732,10018748,10018746,10018734,10018732,10018740,10018732,10018748,10018750,10018734,10018732,10018747,10018732,10018748,10018750,10018734,10018733,10018747,10018733,10018749,10018734,10018733,10018747,10018733,10018749,10018734,10018733,10018747,10018733,10018749,10018734,10018744,10018749,10018735,10018744,10018749,10018735,10018744,10018749,10018735,10018744,10018749,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018735,10018744,10018744,10018744,10018744,10018744</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L21 W18/25; N=153; EHP=11460.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x3,normal:17x19,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x8,swarm:84x42,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L21 W18/25; N=153; EHP=30335.650715; air:2x8,air:11x6,air:12x8,air:13x8,air:14x6,fast:30x5,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x7,medium:123x7,normal:17x19,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>10018754,10018764,10018756,10048717,10018763,10018757,10018754,10018764,10018756,10048717,10018763,10018757,10018754,10018764,10018756,10048717,10018763,10018758,10018754,10018764,10018756,10048717,10018763,10018758,10018754,10018764,10018756,10018751,10018763,10045219,10018754,10018764,10018759,10018751,10018763,10018761,10018754,10018764,10018759,10018751,10018763,10018761,10018754,10018764,10018759,10018751,10018768,10018762,10018754,10018764,10018759,10048718,10018768,10018762,10018754,10018764,10018759,10048718,10018768,10018765,10018754,10018764,10018760,10048718,10018768,10018765,10018754,10018764,10018760,10018752,10018768,10018766,10018754,10018764,10018760,10018752,10018768,10018766,10018754,10018764,10018760,10018752,10018768,10018770,10018754,10018764,10018767,10018752,10018768,10018770,10018754,10018764,10018767,10018753,10018769,10018754,10018764,10018767,10018753,10018769,10018754,10018764,10018767,10018753,10018769,10018754,10018764,10018767,10018753,10018769,10018755,10018764,10018769,10018755,10018764,10018769,10018755,10018764,10018769,10018755,10018764,10018769,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018764,10018764,10018764,10018764,10018764</t>
+          <t>10018754,10048717,10018756,10048717,10018763,10018757,10018754,10048717,10018756,10048717,10018763,10018757,10018754,10048717,10018756,10048717,10018763,10018758,10018754,10048717,10018756,10048717,10018763,10018758,10018754,10018751,10018756,10018751,10018763,10045219,10018754,10018751,10018759,10018751,10018763,10018761,10018754,10018751,10018759,10018751,10018763,10018761,10018754,10018751,10018759,10018751,10018768,10018762,10018754,10048718,10018759,10048718,10018768,10018762,10018754,10048718,10018759,10048718,10018768,10018765,10018754,10048718,10018760,10048718,10018768,10018765,10018754,10018752,10018760,10018752,10018768,10018766,10018754,10018752,10018760,10018752,10018768,10018766,10018754,10018752,10018760,10018752,10018768,10018770,10018754,10018752,10018767,10018752,10018768,10018770,10018754,10018753,10018767,10018753,10018769,10018754,10018753,10018767,10018753,10018769,10018754,10018753,10018767,10018753,10018769,10018754,10018753,10018767,10018753,10018769,10018755,10018764,10018769,10018755,10018764,10018769,10018755,10018764,10018769,10018755,10018764,10018769,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018755,10018764,10018764,10018764,10018764,10018764,10018764</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L21 W19/25; N=159; EHP=13275.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x19,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,heavy:67x1,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x44,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L21 W19/25; N=159; EHP=35148.581186; air:2x8,air:11x8,air:12x6,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x8,medium:123x8,normal:17x19,normal:18x20,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>10018774,10018786,10018776,10048719,10018785,10018777,10018781,10018774,10018786,10018776,10048719,10018785,10018777,10018774,10018786,10018776,10048719,10018785,10018778,10018774,10018786,10018776,10048719,10018785,10018778,10018774,10018786,10018779,10018771,10018785,10018782,10018774,10018786,10018779,10018771,10018785,10018782,10018774,10018786,10018779,10018771,10018785,10018783,10018774,10018786,10018779,10018771,10018785,10018783,10018774,10018786,10018779,10048720,10018789,10018784,10018774,10018786,10018780,10048720,10018789,10018784,10018774,10018786,10018780,10048720,10018789,10018787,10018774,10018786,10018780,10048720,10018789,10018787,10018774,10018786,10018780,10018772,10018789,10045220,10018774,10018786,10018780,10018772,10018789,10045220,10018774,10018786,10018788,10018772,10018789,10018791,10018774,10018786,10018788,10018772,10018789,10018791,10018774,10018786,10018788,10018773,10018790,10018774,10018786,10018788,10018773,10018790,10018774,10018786,10018788,10018773,10018790,10018774,10018786,10018773,10018790,10018775,10018786,10018790,10018775,10018786,10018790,10018775,10018786,10018790,10018775,10018786,10018790,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018786,10018786,10018786,10018786,10018786,10018786,10018786</t>
+          <t>10018774,10048719,10018776,10048719,10018785,10018777,10018781,10018774,10048719,10018776,10048719,10018785,10018777,10018774,10048719,10018776,10048719,10018785,10018778,10018774,10048719,10018776,10048719,10018785,10018778,10018774,10018771,10018779,10018771,10018785,10018782,10018774,10018771,10018779,10018771,10018785,10018782,10018774,10018771,10018779,10018771,10018785,10018783,10018774,10018771,10018779,10018771,10018785,10018783,10018774,10048720,10018779,10048720,10018789,10018784,10018774,10048720,10018780,10048720,10018789,10018784,10018774,10048720,10018780,10048720,10018789,10018787,10018774,10048720,10018780,10048720,10018789,10018787,10018774,10018772,10018780,10018772,10018789,10045220,10018774,10018772,10018780,10018772,10018789,10045220,10018774,10018772,10018788,10018772,10018789,10018791,10018774,10018772,10018788,10018772,10018789,10018791,10018774,10018773,10018788,10018773,10018790,10018774,10018773,10018788,10018773,10018790,10018774,10018773,10018788,10018773,10018790,10018774,10018773,10018773,10018790,10018775,10018786,10018790,10018775,10018786,10018790,10018775,10018786,10018790,10018775,10018786,10018790,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018775,10018786,10018786,10018786,10018786,10018786,10018786,10018786,10018786</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L21 W20/25; N=165; EHP=22283.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x19,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x46,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L21 W20/25; N=165; EHP=58992.380425; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x4,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x19,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10018795,10018805,10018797,10048721,10018804,10018798,10018795,10018805,10018797,10048721,10018804,10018798,10018795,10018805,10018797,10048721,10018804,10018799,10018795,10018805,10018797,10048721,10018804,10018799,10018795,10018805,10018797,10018792,10018804,10018802,10018795,10018805,10018800,10018792,10018804,10018802,10018795,10018805,10018800,10018792,10018804,10018803,10018795,10018805,10018800,10018792,10018804,10018803,10018795,10018805,10018800,10018792,10018804,10045221,10018795,10018805,10018800,10048722,10018809,10045221,10018795,10018805,10018801,10048722,10018809,10018806,10018795,10018805,10018801,10048722,10018809,10018806,10018795,10018805,10018801,10048722,10018809,10018806,10018795,10018805,10018801,10018793,10018809,10018807,10018795,10018805,10018801,10018793,10018809,10018807,10018795,10018805,10018808,10018793,10018809,10018811,10018795,10018805,10018808,10018793,10018809,10018811,10018795,10018805,10018808,10018794,10018810,10018795,10018805,10018808,10018794,10018810,10018795,10018805,10018808,10018794,10018810,10018796,10018805,10018794,10018810,10018796,10018805,10018810,10018796,10018805,10018810,10018796,10018805,10018810,10018796,10018805,10018810,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018805,10018805,10018805,10018805,10018805,10018805</t>
+          <t>10018795,10048721,10018797,10048721,10018804,10018798,10018795,10048721,10018797,10048721,10018804,10018798,10018795,10048721,10018797,10048721,10018804,10018799,10018795,10048721,10018797,10048721,10018804,10018799,10018795,10018792,10018797,10018792,10018804,10018802,10018795,10018792,10018800,10018792,10018804,10018802,10018795,10018792,10018800,10018792,10018804,10018803,10018795,10018792,10018800,10018792,10018804,10018803,10018795,10018792,10018800,10018792,10018804,10045221,10018795,10048722,10018800,10048722,10018809,10045221,10018795,10048722,10018801,10048722,10018809,10018806,10018795,10048722,10018801,10048722,10018809,10018806,10018795,10048722,10018801,10048722,10018809,10018806,10018795,10018793,10018801,10018793,10018809,10018807,10018795,10018793,10018801,10018793,10018809,10018807,10018795,10018793,10018808,10018793,10018809,10018811,10018795,10018793,10018808,10018793,10018809,10018811,10018795,10018794,10018808,10018794,10018810,10018795,10018794,10018808,10018794,10018810,10018795,10018794,10018808,10018794,10018810,10018796,10018794,10018794,10018810,10018796,10018805,10018810,10018796,10018805,10018810,10018796,10018805,10018810,10018796,10018805,10018810,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018796,10018805,10018805,10018805,10018805,10018805,10018805,10018805</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L21 W21/25; N=171; EHP=22729.000000; air:2x4,air:11x5,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x47,heavy:86x3,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L21 W21/25; N=171; EHP=60194.902977; air:2x8,air:11x10,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x8,medium:123x8,normal:17x20,normal:18x21,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10018815,10018826,10018817,10048723,10018825,10018818,10018815,10018826,10018817,10048723,10018825,10018818,10018815,10018826,10018817,10048723,10018825,10018818,10018815,10018826,10018817,10048723,10018825,10018819,10018815,10018826,10018817,10018812,10018825,10018819,10018815,10018826,10018820,10018812,10018825,10018822,10018815,10018826,10018820,10018812,10018825,10018822,10018815,10018826,10018820,10018812,10018825,10018823,10018815,10018826,10018820,10048724,10018830,10018823,10018815,10018826,10018820,10048724,10018830,10018824,10018815,10018826,10018821,10048724,10018830,10018824,10018815,10018826,10018821,10048724,10018830,10018827,10018815,10018826,10018821,10018813,10018830,10018827,10018815,10018826,10018821,10018813,10018830,10018828,10018815,10018826,10018821,10018813,10018830,10018828,10018815,10018826,10018821,10018813,10018830,10018832,10018815,10018826,10018829,10018814,10018830,10018832,10018815,10018826,10018829,10018814,10018831,10018815,10018826,10018829,10018814,10018831,10018815,10018826,10018829,10018814,10018831,10018815,10018826,10018829,10018814,10018831,10018815,10018826,10018831,10018816,10018826,10018831,10018816,10018826,10018831,10018816,10018826,10018831,10018816,10018826,10018831,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018826,10018826,10018826,10018826,10018826,10018826</t>
+          <t>10018815,10048723,10018817,10048723,10018825,10018818,10018815,10048723,10018817,10048723,10018825,10018818,10018815,10048723,10018817,10048723,10018825,10018818,10018815,10048723,10018817,10048723,10018825,10018819,10018815,10018812,10018817,10018812,10018825,10018819,10018815,10018812,10018820,10018812,10018825,10018822,10018815,10018812,10018820,10018812,10018825,10018822,10018815,10018812,10018820,10018812,10018825,10018823,10018815,10048724,10018820,10048724,10018830,10018823,10018815,10048724,10018820,10048724,10018830,10018824,10018815,10048724,10018821,10048724,10018830,10018824,10018815,10048724,10018821,10048724,10018830,10018827,10018815,10018813,10018821,10018813,10018830,10018827,10018815,10018813,10018821,10018813,10018830,10018828,10018815,10018813,10018821,10018813,10018830,10018828,10018815,10018813,10018821,10018813,10018830,10018832,10018815,10018814,10018829,10018814,10018830,10018832,10018815,10018814,10018829,10018814,10018831,10018815,10018814,10018829,10018814,10018831,10018815,10018814,10018829,10018814,10018831,10018815,10018814,10018829,10018814,10018831,10018815,10018826,10018831,10018816,10018826,10018831,10018816,10018826,10018831,10018816,10018826,10018831,10018816,10018826,10018831,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018816,10018826,10018826,10018826,10018826,10018826,10018826,10018826</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L21 W22/25; N=177; EHP=23184.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x5,normal:17x22,normal:18x21,fast:30x5,heavy:31x3,heavy:40x2,fast:58x5,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x49,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L21 W22/25; N=177; EHP=61377.107671; air:2x8,air:11x8,air:12x8,air:13x8,air:14x10,fast:30x5,fast:58x5,fast:64x6,fast:98x5,heavy:31x3,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x9,medium:123x9,normal:17x22,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10018836,10018847,10018838,10048725,10018846,10018839,10018836,10018847,10018838,10048725,10018846,10018839,10018836,10018847,10018838,10048725,10018846,10018840,10018836,10018847,10018838,10048725,10018846,10018840,10018836,10018847,10018838,10048725,10018846,10018840,10018836,10018847,10018838,10018833,10018846,10018843,10018836,10018847,10018841,10018833,10018846,10018843,10018836,10018847,10018841,10018833,10018846,10018844,10018836,10018847,10018841,10018833,10018846,10018844,10018836,10018847,10018841,10048726,10018851,10018845,10018836,10018847,10018841,10048726,10018851,10018845,10018836,10018847,10018842,10048726,10018851,10018848,10018836,10018847,10018842,10048726,10018851,10018848,10018836,10018847,10018842,10048726,10018851,10018849,10018836,10018847,10018842,10018834,10018851,10018849,10018836,10018847,10018842,10018834,10018851,10018853,10018836,10018847,10018850,10018834,10018851,10018853,10018836,10018847,10018850,10018834,10018851,10018853,10018836,10018847,10018850,10018835,10018852,10018836,10018847,10018850,10018835,10018852,10018836,10018847,10018850,10018835,10018852,10018836,10018847,10018835,10018852,10018837,10018847,10018852,10018837,10018847,10018852,10018837,10018847,10018852,10018837,10018847,10018852,10018837,10018847,10018852,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018847,10018847,10018847,10018847,10018847,10018847,10018847</t>
+          <t>10018836,10048725,10018838,10048725,10018846,10018839,10018836,10048725,10018838,10048725,10018846,10018839,10018836,10048725,10018838,10048725,10018846,10018840,10018836,10048725,10018838,10048725,10018846,10018840,10018836,10048725,10018838,10048725,10018846,10018840,10018836,10018833,10018838,10018833,10018846,10018843,10018836,10018833,10018841,10018833,10018846,10018843,10018836,10018833,10018841,10018833,10018846,10018844,10018836,10018833,10018841,10018833,10018846,10018844,10018836,10048726,10018841,10048726,10018851,10018845,10018836,10048726,10018841,10048726,10018851,10018845,10018836,10048726,10018842,10048726,10018851,10018848,10018836,10048726,10018842,10048726,10018851,10018848,10018836,10048726,10018842,10048726,10018851,10018849,10018836,10018834,10018842,10018834,10018851,10018849,10018836,10018834,10018842,10018834,10018851,10018853,10018836,10018834,10018850,10018834,10018851,10018853,10018836,10018834,10018850,10018834,10018851,10018853,10018836,10018835,10018850,10018835,10018852,10018836,10018835,10018850,10018835,10018852,10018836,10018835,10018850,10018835,10018852,10018836,10018835,10018835,10018852,10018837,10018847,10018852,10018837,10018847,10018852,10018837,10018847,10018852,10018837,10018847,10018852,10018837,10018847,10018852,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018837,10018847,10018847,10018847,10018847,10018847,10018847,10018847,10018847</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L21 W23/25; N=183; EHP=23648.000000; air:2x5,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x22,normal:18x22,fast:30x6,heavy:31x2,heavy:40x3,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x51,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x3</t>
+          <t>L21 W23/25; N=183; EHP=62613.299270; air:2x10,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x6,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10018857,10018868,10018859,10048727,10018867,10018860,10018857,10018868,10018859,10048727,10018867,10018860,10018857,10018868,10018859,10048727,10018867,10018861,10018857,10018868,10018859,10048727,10018867,10018861,10018857,10018868,10018859,10048727,10018867,10018864,10018857,10018868,10018862,10018854,10018867,10018864,10018857,10018868,10018862,10018854,10018867,10018865,10018857,10018868,10018862,10018854,10018867,10018865,10018857,10018868,10018862,10018854,10018867,10018865,10018857,10018868,10018862,10018854,10018867,10018866,10018857,10018868,10018862,10048728,10018872,10018866,10018857,10018868,10018863,10048728,10018872,10018869,10018857,10018868,10018863,10048728,10018872,10018869,10018857,10018868,10018863,10048728,10018872,10018870,10018857,10018868,10018863,10018855,10018872,10018870,10018857,10018868,10018863,10018855,10018872,10018874,10018857,10018868,10018871,10018855,10018872,10018874,10018857,10018868,10018871,10018855,10018872,10018874,10018857,10018868,10018871,10018855,10018872,10018857,10018868,10018871,10018856,10018873,10018857,10018868,10018871,10018856,10018873,10018857,10018868,10018871,10018856,10018873,10018857,10018868,10018856,10018873,10018858,10018868,10018873,10018858,10018868,10018873,10018858,10018868,10018873,10018858,10018868,10018873,10018858,10018868,10018873,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018868,10018868,10018868,10018868,10018868,10018868</t>
+          <t>10018857,10048727,10018859,10048727,10018867,10018860,10018857,10048727,10018859,10048727,10018867,10018860,10018857,10048727,10018859,10048727,10018867,10018861,10018857,10048727,10018859,10048727,10018867,10018861,10018857,10048727,10018859,10048727,10018867,10018864,10018857,10018854,10018862,10018854,10018867,10018864,10018857,10018854,10018862,10018854,10018867,10018865,10018857,10018854,10018862,10018854,10018867,10018865,10018857,10018854,10018862,10018854,10018867,10018865,10018857,10018854,10018862,10018854,10018867,10018866,10018857,10048728,10018862,10048728,10018872,10018866,10018857,10048728,10018863,10048728,10018872,10018869,10018857,10048728,10018863,10048728,10018872,10018869,10018857,10048728,10018863,10048728,10018872,10018870,10018857,10018855,10018863,10018855,10018872,10018870,10018857,10018855,10018863,10018855,10018872,10018874,10018857,10018855,10018871,10018855,10018872,10018874,10018857,10018855,10018871,10018855,10018872,10018874,10018857,10018855,10018871,10018855,10018872,10018857,10018856,10018871,10018856,10018873,10018857,10018856,10018871,10018856,10018873,10018857,10018856,10018871,10018856,10018873,10018857,10018856,10018856,10018873,10018858,10018868,10018873,10018858,10018868,10018873,10018858,10018868,10018873,10018858,10018868,10018873,10018858,10018868,10018873,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018858,10018868,10018868,10018868,10018868,10018868,10018868,10018868</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L21 W24/25; N=189; EHP=25323.000000; air:2x5,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x23,normal:18x23,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x5,heavy:67x2,heavy:70x3,heavy:80x2,medium:83x10,swarm:84x52,heavy:86x2,heavy:88x2,fast:98x6,medium:108x9,medium:123x9,heavy:127x3</t>
+          <t>L21 W24/25; N=189; EHP=67059.968685; air:2x10,air:11x10,air:12x8,air:13x10,air:14x8,fast:30x5,fast:58x6,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x10,medium:108x9,medium:123x9,normal:17x23,normal:18x23,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10018878,10018889,10018880,10048729,10018888,10018881,10018896,10018878,10018889,10018880,10048729,10018888,10018881,10018878,10018889,10018880,10048729,10018888,10018882,10018878,10018889,10018880,10048729,10018888,10018882,10018878,10018889,10018880,10018875,10018888,10018885,10018878,10018889,10018880,10018875,10018888,10018885,10018878,10018889,10018883,10018875,10018888,10018885,10018878,10018889,10018883,10018875,10018888,10018886,10018878,10018889,10018883,10018875,10018888,10018886,10018878,10018889,10018883,10048730,10018893,10018886,10018878,10018889,10018883,10048730,10018893,10018887,10018878,10018889,10018883,10048730,10018893,10018887,10018878,10018889,10018884,10048730,10018893,10018890,10018878,10018889,10018884,10018876,10018893,10018890,10018878,10018889,10018884,10018876,10018893,10018891,10018878,10018889,10018884,10018876,10018893,10018891,10018878,10018889,10018884,10018876,10018893,10018891,10018878,10018889,10018884,10018876,10018893,10018895,10018878,10018889,10018892,10018877,10018893,10018895,10018878,10018889,10018892,10018877,10018894,10018878,10018889,10018892,10018877,10018894,10018878,10018889,10018892,10018877,10018894,10018878,10018889,10018892,10018877,10018894,10018879,10018889,10018894,10018879,10018889,10018894,10018879,10018889,10018894,10018879,10018889,10018894,10018879,10018889,10018894,10018879,10018889,10018894,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018889,10018889,10018889,10018889,10018889,10018889,10018889,10018889</t>
+          <t>10018878,10048729,10018880,10048729,10018888,10018881,10018896,10018878,10048729,10018880,10048729,10018888,10018881,10018878,10048729,10018880,10048729,10018888,10018882,10018878,10048729,10018880,10048729,10018888,10018882,10018878,10018875,10018880,10018875,10018888,10018885,10018878,10018875,10018880,10018875,10018888,10018885,10018878,10018875,10018883,10018875,10018888,10018885,10018878,10018875,10018883,10018875,10018888,10018886,10018878,10018875,10018883,10018875,10018888,10018886,10018878,10048730,10018883,10048730,10018893,10018886,10018878,10048730,10018883,10048730,10018893,10018887,10018878,10048730,10018883,10048730,10018893,10018887,10018878,10048730,10018884,10048730,10018893,10018890,10018878,10018876,10018884,10018876,10018893,10018890,10018878,10018876,10018884,10018876,10018893,10018891,10018878,10018876,10018884,10018876,10018893,10018891,10018878,10018876,10018884,10018876,10018893,10018891,10018878,10018876,10018884,10018876,10018893,10018895,10018878,10018877,10018892,10018877,10018893,10018895,10018878,10018877,10018892,10018877,10018894,10018878,10018877,10018892,10018877,10018894,10018878,10018877,10018892,10018877,10018894,10018878,10018877,10018892,10018877,10018894,10018879,10018889,10018894,10018879,10018889,10018894,10018879,10018889,10018894,10018879,10018889,10018894,10018879,10018889,10018894,10018879,10018889,10018894,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018879,10018889,10018889,10018889,10018889,10018889,10018889,10018889,10018889,10018889</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L21 W25/25; N=195; EHP=50541.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x5,normal:17x23,normal:18x23,fast:30x6,heavy:31x2,heavy:40x2,fast:58x6,fast:64x6,heavy:67x3,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x54,heavy:86x2,heavy:88x3,fast:98x5,medium:108x10,medium:123x10,heavy:127x2,boss:132x1</t>
+          <t>L21 W25/25; N=195; EHP=133759.070498; air:2x8,air:11x10,air:12x8,air:13x10,air:14x10,boss:132x1,fast:30x6,fast:58x6,fast:64x6,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x9,medium:108x10,medium:123x10,normal:17x23,normal:18x23,swarm:84x31 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L21/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L21/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>240</v>
+        <v>350</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>233</v>
+        <v>320</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>226</v>
+        <v>280</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>219</v>
+        <v>360</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>212</v>
+        <v>310</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>205</v>
+        <v>290</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>191</v>
+        <v>300</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>184</v>
+        <v>280</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>177</v>
+        <v>360</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>170</v>
+        <v>290</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>163</v>
+        <v>310</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>156</v>
+        <v>280</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>149</v>
+        <v>205</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>142</v>
+        <v>300</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>135</v>
+        <v>280</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>128</v>
+        <v>360</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>128</v>
+        <v>270</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>260</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>200</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>360</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
